--- a/tc6.xlsx
+++ b/tc6.xlsx
@@ -425,126 +425,1672 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Scenario ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>Scenario Title</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Attachments</t>
+          <t>Test Case ID</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Test Case Title</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Test Case Type</t>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Test Type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Automation Feasible</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Step #</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Test Step Description</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Precondition Test Step Expected Result Test Case Attachment</t>
+          <t>TC001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Test Step #</t>
+          <t>US32275</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Test Step Description</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>Plan Recommendation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Verify side-by-side plan comparison</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>User is logged into the CareSource enrollment portal and has completed the health needs questionnaire</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>User with completed profile and at least two recommended plans</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Navigate to plan recommendation page</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>System displays side-by-side comparison of at least two plans highlighting premiums, deductibles, co-pays, out-of-pocket maximums, and coverage for specified medications and doctors</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Verify Valid EDI 270 Inquiry File Generation for Delinquency Status Positive System configured with trading partner IDs for Availity, ETSPassport, Dorado, Instamed. Valid subscriber data available. sample_input_270.json generated_270_01.txt</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TC-EDI270-271-DEL-001 Generate a valid EDI 270 eligibility inquiry file with correct ISA/GS headers, 2000C subscriber loop with patient details, and ensure the file is properly formatted for the four trading partners. Verify all mandatory segments (ISA, GS, ST, BHT, HL, NM1, DMG, DTP) are present and data elements comply with the specification. 1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>sample_edi270_valid_01.txt Prepare valid subscriber and provider input data including member ID, name, DOB, gender, and trading partner ID.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Draft Input data is prepared with correct formats and trading partner identifiers. 2 3</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Review plan features and select a plan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Selected plan is highlighted and user can proceed to enrollment</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>270_schema_validation_report.json</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>TC002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>US32275</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Plan Recommendation</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Verify navigation to enrollment after plan selection</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>User is on the plan comparison page</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>User with at least one recommended plan</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Select a plan and click 'Enroll'</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>System transitions to the enrollment process with the chosen plan pre-selected</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Verify 271 Response File Includes Delinquency Status EB01=5 (Active - Pending Investigation) Valid 270 inquiry submitted for member with delinquency status active within 0-30 days. generated_271_01.txt</t>
+          <t>TC003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TC-EDI270-271-DEL-002 1</t>
+          <t>US32275</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sample_edi271_valid_01.txt Receive the 271 response file corresponding to the 270 inquiry.</t>
+          <t>Plan Recommendation</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Draft 271 file is received containing loop 2110C with EB segment having EB01 = "5". 2</t>
+          <t>Negative - No recommended plans</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Positive Validate the 271 file against the ANSI X12 271 schema and implementation guide.</t>
+          <t>User has completed health needs but no plans match criteria</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>User with uncommon criteria resulting in no matches</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Navigate to plan recommendation page</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>System displays a message: "No plans match your criteria. Please adjust your preferences."</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>271_schema_validation_report.json</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>TC004</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>US32275</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Plan Recommendation</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Edge - Maximum number of plans</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>User qualifies for 10+ plans</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>User with broad criteria resulting in maximum recommendations</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Navigate to plan recommendation page</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>System displays all recommended plans in a scrollable, readable format without UI breakage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC005</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>US32274</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Verify member can input medications and providers</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Medication: Metformin 500mg, Provider: Dr. Smith</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Navigate to health needs input page</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>System displays input fields for medications and providers</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Enter medication and provider information and submit</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>System accepts input, validates data, and confirms successful entry</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC006</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>US32274</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Verify financial preference input</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Premium: $200, Deductible: $1000, OOP Max: $5000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Navigate to financial preferences section</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>System displays fields for premium, deductible, and out-of-pocket maximum</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Enter preferences and submit</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>System saves preferences and updates recommendation criteria</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC007</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>US32274</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Negative - Invalid medication entry</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Medication: "" (blank entry)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Leave medication field blank and submit</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>System displays error: "Medication name required"</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC008</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>US32274</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Plan Personalization</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Edge - Large medication list</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>User is authenticated</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Medication: 20+ entries</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Enter 20+ medications and submit</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>System accepts all entries and processes recommendations without error</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC009</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>US32273</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Guided Enrollment</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Verify guided workflow for plan selection</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Health: Asthma, PCP: Dr. Lee, Premium: $150</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Start guided enrollment</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>System prompts for health data, provider, and financial preferences in sequence</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Complete all steps and submit</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>System generates and displays personalized plan recommendations with comparison tool</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC010</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>US32273</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Guided Enrollment</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Negative - Missing required fields</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Omit required health data</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Attempt to proceed without entering all required fields</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>System displays validation errors for missing fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC011</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>US32273</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Guided Enrollment</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Edge - Extreme cost preferences</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Premium: $0, Deductible: $0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Enter extreme values and submit</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>System processes and displays only plans meeting criteria, or a message if none available</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC012</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>US31822</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Demographic Input</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Verify demographic and health needs input</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Age: 40, Location: OH, Doctor: Dr. Adams, Medication: Lisinopril</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Navigate to demographic input page</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>System displays fields for age, location, doctors, medications</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Enter data and submit</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>System validates and accepts input, proceeding to recommendations</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC013</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>US31822</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Demographic Input</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Negative - Invalid age</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Age: -1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Enter invalid age and submit</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>System displays error: "Invalid age"</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC014</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>US31822</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Demographic Input</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Edge - Maximum field length</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>User is a prospective member</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Doctor name: 100+ characters</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Enter maximum length for doctor name and submit</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>System accepts or displays appropriate error without crashing</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC015</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>US32306</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Verify profile view</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>User with profile data</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Navigate to profile page</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>System displays correct profile information</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC016</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>US32307</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Verify settings update</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>New notification preference</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Go to settings, change preference, save</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>System updates and confirms setting change</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC017</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>US32308</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Transaction History</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Verify transaction history view</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>User with transaction history</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Navigate to transaction history</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>System displays all past transactions</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TC018</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>US32309</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Search and Filter</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Verify data search and filter</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Search: "Diabetes", Filter: Date range</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Enter search term and filter</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>System returns correct filtered data</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC019</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>US32310</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Export Reports</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Verify report export</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Report: Claims</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Click export on claims report</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>System downloads report in selected format</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC020</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>US32311</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>User Permissions</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Verify permission management</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Admin user logged in</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Assign 'Editor' to user X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Navigate to permissions, assign role</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>System saves and reflects new permission</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TC021</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>US32312</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>System Logs</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Verify system log view</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Admin user logged in</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Any log record</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Navigate to system logs</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>System displays logs with timestamp, user, action</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TC022</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>US32304</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Password Reset</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Verify password reset</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>User on login page</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Registered email</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Click 'Forgot Password', enter email</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>System sends reset link to email</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TC023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>US32305</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Two-Factor Authentication</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Verify 2FA enablement</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Valid phone number</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Navigate to security, enable 2FA</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>System sends code and confirms setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TC024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>US32303</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Verify email login</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>User is registered</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Valid email/password</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Enter credentials, click login</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>System authenticates and redirects to dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TC025</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>US32983</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NEW STORY TETS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Basic smoke test</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>System available</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Access feature</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Feature loads without error</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TC026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>US32744</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>member 1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Basic smoke test</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>System available</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Access feature</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Feature loads without error</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
